--- a/astro-site/public/dl/chocolate-shop-checklist-templates/09-cash-drawer-opening-closing.xlsx
+++ b/astro-site/public/dl/chocolate-shop-checklist-templates/09-cash-drawer-opening-closing.xlsx
@@ -1927,7 +1927,7 @@
       </c>
       <c r="B15" s="31" t="inlineStr">
         <is>
-          <t>Log the deposits collected on pre-orders and the list of pre-orders awaiting pickup (not the day's sales)</t>
+          <t>Ring pre-order deposits on the POS as deposits (not the day's sales) so the over/short stays right, and update the list of pre-orders awaiting pickup</t>
         </is>
       </c>
       <c r="C15" s="32" t="inlineStr">
